--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git_repositories\mlogger\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DFBCD09-48DE-4741-9F75-10EB085A3F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26134B3B-9AC1-4534-8D42-55DF20656B05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="41460" yWindow="820" windowWidth="17280" windowHeight="14360" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="4" r:id="rId1"/>
@@ -112,12 +112,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>IC201</t>
-  </si>
-  <si>
-    <t>C804, C805</t>
-  </si>
-  <si>
     <t>MFU0603FF01000P500</t>
     <phoneticPr fontId="19"/>
   </si>
@@ -271,9 +265,6 @@
     <t>TE Connectivity Passive Product</t>
   </si>
   <si>
-    <t>https://www.digikey.jp/ja/products/detail/te-connectivity-passive-product/RQ73C1J232RBTD/9480531</t>
-  </si>
-  <si>
     <t>Diotec Semiconductor</t>
   </si>
   <si>
@@ -484,9 +475,6 @@
   <si>
     <t>C1, C2, C3</t>
     <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>J02</t>
   </si>
   <si>
     <t>JST Sales America Inc.</t>
@@ -882,6 +870,22 @@
     <t>https://www.digikey.jp/ja/products/detail/torex-semiconductor-ltd/XCL102D503CR-G/7361182</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
+  <si>
+    <t>C804, C805</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>IC201</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>J02</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/te-connectivity-passive-product/RQ73C1J232RBTD/9480531</t>
+    <phoneticPr fontId="19"/>
+  </si>
 </sst>
 </file>
 
@@ -892,7 +896,7 @@
     <numFmt numFmtId="8" formatCode="&quot;¥&quot;#,##0.00;[Red]&quot;¥&quot;\-#,##0.00"/>
     <numFmt numFmtId="176" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1067,12 +1071,6 @@
     <font>
       <sz val="12"/>
       <name val="ＭＳ ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <charset val="128"/>
     </font>
@@ -1558,7 +1556,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1587,26 +1585,23 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="43" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="8" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="43" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="43" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -1982,57 +1977,57 @@
     <col min="8" max="16384" width="11" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="17" t="s">
+    <row r="1" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="17" t="s">
+      <c r="C1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="G1" s="17" t="s">
+      <c r="F1" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1" s="16" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A2" s="6">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C2" s="4">
         <f t="shared" ref="C2:C28" si="0">LEN(B2) - LEN(SUBSTITUTE(B2,",",""))+1</f>
         <v>2</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.5">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A3" s="6">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" si="0"/>
@@ -2042,21 +2037,21 @@
         <v>6</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A4" s="6">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="0"/>
@@ -2066,45 +2061,45 @@
         <v>6</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A5" s="6">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.5">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A6" s="6">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>205</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="0"/>
@@ -2114,21 +2109,21 @@
         <v>6</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A7" s="6">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="0"/>
@@ -2138,21 +2133,21 @@
         <v>6</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.5">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A8" s="6">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C8" s="4">
         <f t="shared" si="0"/>
@@ -2162,19 +2157,19 @@
         <v>9</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.5">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A9" s="6">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="0"/>
@@ -2184,21 +2179,21 @@
         <v>15</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.5">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A10" s="6">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" si="0"/>
@@ -2208,43 +2203,43 @@
         <v>15</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A11" s="6">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C11" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.5">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A12" s="6">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C12" s="4">
         <f t="shared" si="0"/>
@@ -2254,91 +2249,91 @@
         <v>15</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A13" s="6">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C13" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A14" s="6">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C14" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.5">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A15" s="6">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>18</v>
+        <v>206</v>
       </c>
       <c r="C15" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.5">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A16" s="6">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C16" s="4">
         <f t="shared" si="0"/>
@@ -2348,135 +2343,135 @@
         <v>5</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.5">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A17" s="6">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C17" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.5">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A18" s="6">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.5">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A19" s="6">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.5">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A20" s="6">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>114</v>
+        <v>207</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.5">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A21" s="6">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C21" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D21" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="F21" s="16" t="s">
-        <v>182</v>
+      <c r="D21" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>178</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.5">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A22" s="6">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C22" s="4">
         <f t="shared" si="0"/>
@@ -2486,21 +2481,21 @@
         <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A23" s="6">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C23" s="4">
         <f t="shared" si="0"/>
@@ -2510,74 +2505,74 @@
         <v>12</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.5">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A24" s="6">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C24" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.5">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A25" s="6">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C25" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.5">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A26" s="6">
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C26" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>11</v>
@@ -2585,36 +2580,36 @@
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
     </row>
-    <row r="27" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A27" s="6">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C27" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.5">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A28" s="6">
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C28" s="4">
         <f t="shared" si="0"/>
@@ -2627,19 +2622,14 @@
         <v>10</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="8"/>
+        <v>177</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="D30" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
@@ -2667,25 +2657,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="12" t="s">
+      <c r="A1" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="12" t="s">
+      <c r="C1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="G1" s="12" t="s">
+      <c r="F1" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1" s="11" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2694,7 +2684,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C2" s="4">
         <f t="shared" ref="C2:C20" si="0">LEN(B2) - LEN(SUBSTITUTE(B2,",",""))+1</f>
@@ -2704,22 +2694,22 @@
         <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="15"/>
+      <c r="I2" s="14"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A3" s="6">
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" si="0"/>
@@ -2729,22 +2719,22 @@
         <v>6</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I3" s="15"/>
+        <v>39</v>
+      </c>
+      <c r="I3" s="14"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A4" s="6">
         <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="0"/>
@@ -2754,22 +2744,22 @@
         <v>6</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="15"/>
+      <c r="I4" s="14"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A5" s="6">
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="0"/>
@@ -2777,72 +2767,72 @@
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="I5" s="15"/>
+        <v>106</v>
+      </c>
+      <c r="I5" s="14"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A6" s="6">
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="I6" s="15"/>
+        <v>204</v>
+      </c>
+      <c r="I6" s="14"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A7" s="6">
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I7" s="15"/>
+        <v>101</v>
+      </c>
+      <c r="I7" s="14"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A8" s="6">
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C8" s="4">
         <f t="shared" si="0"/>
@@ -2852,43 +2842,43 @@
         <v>5</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I8" s="15"/>
+        <v>98</v>
+      </c>
+      <c r="I8" s="14"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A9" s="6">
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D9" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>63</v>
+      <c r="D9" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>60</v>
       </c>
       <c r="F9" s="2"/>
-      <c r="G9" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="I9" s="15"/>
+      <c r="G9" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="I9" s="14"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A10" s="6">
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" si="0"/>
@@ -2902,255 +2892,255 @@
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" s="15"/>
+        <v>23</v>
+      </c>
+      <c r="I10" s="14"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A11" s="6">
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C11" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D11" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>61</v>
+      <c r="D11" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="I11" s="15"/>
+        <v>62</v>
+      </c>
+      <c r="I11" s="14"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A12" s="6">
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C12" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11" t="s">
-        <v>170</v>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10" t="s">
+        <v>166</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I12" s="15"/>
+        <v>92</v>
+      </c>
+      <c r="I12" s="14"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A13" s="6">
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C13" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D13" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>169</v>
+      <c r="D13" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>165</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I13" s="15"/>
+        <v>68</v>
+      </c>
+      <c r="I13" s="14"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A14" s="6">
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C14" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D14" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>168</v>
+      <c r="D14" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>164</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="I14" s="15"/>
+        <v>208</v>
+      </c>
+      <c r="I14" s="14"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A15" s="6">
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C15" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D15" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>167</v>
+      <c r="D15" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>163</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I15" s="15"/>
+        <v>88</v>
+      </c>
+      <c r="I15" s="14"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A16" s="6">
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C16" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D16" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>166</v>
+      <c r="D16" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>162</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I16" s="15"/>
+        <v>86</v>
+      </c>
+      <c r="I16" s="14"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A17" s="6">
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C17" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D17" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>165</v>
+      <c r="D17" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>161</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I17" s="15"/>
+        <v>84</v>
+      </c>
+      <c r="I17" s="14"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A18" s="6">
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11" t="s">
-        <v>164</v>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10" t="s">
+        <v>160</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I18" s="15"/>
+        <v>71</v>
+      </c>
+      <c r="I18" s="14"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A19" s="6">
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="I19" s="15"/>
+        <v>198</v>
+      </c>
+      <c r="I19" s="14"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A20" s="6">
         <v>19</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>84</v>
+      <c r="B20" s="6" t="s">
+        <v>81</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E20" s="2">
         <v>32208551</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I20" s="15"/>
+        <v>70</v>
+      </c>
+      <c r="I20" s="14"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.5">
       <c r="F22" s="8"/>
-      <c r="G22" s="14"/>
+      <c r="G22" s="13"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.5">
       <c r="F23" s="8"/>
@@ -3193,32 +3183,32 @@
     <col min="7" max="16384" width="11" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="13" t="s">
+    <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="13" t="s">
+      <c r="C1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
+      <c r="F1" s="12" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A2" s="6">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C2" s="4">
         <f t="shared" ref="C2:C6" si="0">LEN(B2) - LEN(SUBSTITUTE(B2,",",""))+1</f>
@@ -3228,314 +3218,187 @@
         <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A3" s="6">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A4" s="6">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A5" s="6">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A6" s="6">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
+        <v>199</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.5">
       <c r="F7" s="8"/>
     </row>
-    <row r="8" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="9"/>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="D8" s="17"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.5">
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.5">
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.5">
       <c r="F11" s="8"/>
     </row>
-    <row r="12" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.5">
       <c r="F12" s="8"/>
     </row>
-    <row r="13" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.5">
       <c r="F13" s="8"/>
     </row>
-    <row r="14" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.5">
       <c r="F14" s="8"/>
     </row>
-    <row r="15" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.5">
       <c r="F15" s="8"/>
     </row>
-    <row r="16" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.5">
       <c r="F16" s="8"/>
     </row>
-    <row r="17" spans="2:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.5">
       <c r="F17" s="8"/>
     </row>
-    <row r="18" spans="2:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
+    <row r="18" spans="6:6" x14ac:dyDescent="0.5">
       <c r="F18" s="8"/>
     </row>
-    <row r="19" spans="2:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
+    <row r="19" spans="6:6" x14ac:dyDescent="0.5">
       <c r="F19" s="8"/>
     </row>
-    <row r="20" spans="2:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
+    <row r="20" spans="6:6" x14ac:dyDescent="0.5">
       <c r="F20" s="8"/>
     </row>
-    <row r="21" spans="2:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
+    <row r="21" spans="6:6" x14ac:dyDescent="0.5">
       <c r="F21" s="8"/>
     </row>
-    <row r="22" spans="2:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
+    <row r="22" spans="6:6" x14ac:dyDescent="0.5">
       <c r="F22" s="8"/>
     </row>
-    <row r="23" spans="2:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
+    <row r="23" spans="6:6" x14ac:dyDescent="0.5">
       <c r="F23" s="8"/>
     </row>
-    <row r="24" spans="2:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
+    <row r="24" spans="6:6" x14ac:dyDescent="0.5">
       <c r="F24" s="8"/>
     </row>
-    <row r="25" spans="2:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
+    <row r="25" spans="6:6" x14ac:dyDescent="0.5">
       <c r="F25" s="8"/>
     </row>
-    <row r="26" spans="2:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
+    <row r="26" spans="6:6" x14ac:dyDescent="0.5">
       <c r="F26" s="8"/>
     </row>
-    <row r="27" spans="2:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
+    <row r="27" spans="6:6" x14ac:dyDescent="0.5">
       <c r="F27" s="8"/>
     </row>
-    <row r="28" spans="2:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
+    <row r="28" spans="6:6" x14ac:dyDescent="0.5">
       <c r="F28" s="8"/>
     </row>
-    <row r="29" spans="2:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
+    <row r="29" spans="6:6" x14ac:dyDescent="0.5">
       <c r="F29" s="8"/>
     </row>
-    <row r="30" spans="2:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
+    <row r="30" spans="6:6" x14ac:dyDescent="0.5">
       <c r="F30" s="8"/>
     </row>
-    <row r="31" spans="2:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
+    <row r="31" spans="6:6" x14ac:dyDescent="0.5">
       <c r="F31" s="8"/>
     </row>
-    <row r="32" spans="2:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
+    <row r="32" spans="6:6" x14ac:dyDescent="0.5">
       <c r="F32" s="8"/>
     </row>
-    <row r="33" spans="2:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
+    <row r="33" spans="6:6" x14ac:dyDescent="0.5">
       <c r="F33" s="8"/>
     </row>
-    <row r="34" spans="2:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
+    <row r="34" spans="6:6" x14ac:dyDescent="0.5">
       <c r="F34" s="8"/>
     </row>
-    <row r="35" spans="2:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
+    <row r="35" spans="6:6" x14ac:dyDescent="0.5">
       <c r="F35" s="8"/>
     </row>
-    <row r="36" spans="2:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
+    <row r="36" spans="6:6" x14ac:dyDescent="0.5">
       <c r="F36" s="8"/>
     </row>
-    <row r="37" spans="2:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
+    <row r="37" spans="6:6" x14ac:dyDescent="0.5">
       <c r="F37" s="8"/>
     </row>
-    <row r="38" spans="2:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
+    <row r="38" spans="6:6" x14ac:dyDescent="0.5">
       <c r="F38" s="8"/>
     </row>
   </sheetData>

--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git_repositories\mlogger\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26134B3B-9AC1-4534-8D42-55DF20656B05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3F54E0-BF74-4705-B323-07018ED874D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41460" yWindow="820" windowWidth="17280" windowHeight="14360" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="42600" yWindow="2050" windowWidth="28800" windowHeight="15200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="4" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="th_plobe" sheetId="6" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">main!$A$1:$F$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">main!$A$1:$F$29</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">th_plobe!$A$1:$F$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">vel_plobe!$A$1:$F$20</definedName>
   </definedNames>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="222">
   <si>
     <t>Designator</t>
     <phoneticPr fontId="18" type="noConversion"/>
@@ -265,26 +265,12 @@
     <t>TE Connectivity Passive Product</t>
   </si>
   <si>
-    <t>Diotec Semiconductor</t>
-  </si>
-  <si>
-    <t>MMBT3904</t>
-  </si>
-  <si>
     <t>Microchip Technology</t>
   </si>
   <si>
     <t>MCP6V02-E/MD</t>
   </si>
   <si>
-    <t>BAT1, BAT2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/diotec-semiconductor/MMBT3904/13163698</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>RB160M-60</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -317,10 +303,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.digikey.jp/ja/products/detail/yageo/RC0603FR-074K7L/727212</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>YAGEO</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -437,19 +419,7 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.digikey.jp/ja/products/detail/toshiba-semiconductor-and-storage/TCR2EF20-LM-CT/5977733</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>TCR2EF20,LM</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>I2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>XCL102D503CR-G</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -724,10 +694,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>SHT40-BD1B</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>SHT40-AD1B</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -804,17 +770,10 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.lcsc.com/product-detail/C2979179.html</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>MYOUNG</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>MY-AA-04</t>
-  </si>
-  <si>
     <t>G-Switch</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -830,24 +789,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>GREENCONN</t>
-  </si>
-  <si>
-    <t>GREENCONN</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>GPFD101-0401A003R1BH</t>
-  </si>
-  <si>
-    <t>GPFD101-0401A003R1BH</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.lcsc.com/product-detail/C7434680.html</t>
-    <phoneticPr fontId="19"/>
-  </si>
-  <si>
     <t>1 x 4 (2mm)</t>
   </si>
   <si>
@@ -867,10 +808,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.digikey.jp/ja/products/detail/torex-semiconductor-ltd/XCL102D503CR-G/7361182</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>C804, C805</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -885,6 +822,126 @@
   <si>
     <t>https://www.digikey.jp/ja/products/detail/te-connectivity-passive-product/RQ73C1J232RBTD/9480531</t>
     <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>D1</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C393373.html</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>onsemi</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>NUP2114UCMR6T1G</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/sensirion-ag/SHT40-AD1B-R3/14322709</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/sensirion-ag/STCC4-D-R3/26769073</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>GCM188R71H104KA57D</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C85864.html</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>JSCJ</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>JSCJ MMBT3904(RANGE:100-300)</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C20526.html</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Samsung Electro-Mechanics</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>CL21A106KAYNNNE</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C15850.html</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>CL10A105KB8NNNC</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C15849.html</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCR3UF20A,LM(CT</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C7067134.html</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>XCL103D503CR-G</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C5439677.html</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>XKB Connection</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>XKB Connection</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>X4611WRS-04I-C40D28</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>X4611WRS-04I-C40D28</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C917591.html</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>YAGEO</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C99782.html</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C5290182.html</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>BH-AA-B5BA015</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>BAT1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1965,7 +2022,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50CA3BD8-2779-45F6-AE49-6AE2C3B11080}">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="3.7265625" style="7" bestFit="1" customWidth="1"/>
@@ -1994,7 +2051,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="G1" s="16" t="s">
         <v>2</v>
@@ -2005,21 +2062,20 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>61</v>
+        <v>221</v>
       </c>
       <c r="C2" s="4">
-        <f t="shared" ref="C2:C28" si="0">LEN(B2) - LEN(SUBSTITUTE(B2,",",""))+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>187</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.5">
@@ -2027,20 +2083,20 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C3" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="C2:C29" si="0">LEN(B3) - LEN(SUBSTITUTE(B3,",",""))+1</f>
         <v>6</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>14</v>
@@ -2051,7 +2107,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="0"/>
@@ -2061,10 +2117,10 @@
         <v>6</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>17</v>
@@ -2075,7 +2131,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="0"/>
@@ -2085,10 +2141,10 @@
         <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>39</v>
@@ -2099,7 +2155,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="0"/>
@@ -2109,13 +2165,13 @@
         <v>6</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.5">
@@ -2123,7 +2179,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="0"/>
@@ -2133,13 +2189,13 @@
         <v>6</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.5">
@@ -2161,7 +2217,7 @@
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.5">
@@ -2169,23 +2225,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>47</v>
+        <v>192</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>15</v>
+        <v>194</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>49</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.5">
@@ -2193,7 +2247,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" si="0"/>
@@ -2203,13 +2257,13 @@
         <v>15</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.5">
@@ -2217,21 +2271,23 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="C11" s="4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>115</v>
+        <v>15</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" s="2"/>
+        <v>122</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>121</v>
+      </c>
       <c r="G11" s="2" t="s">
-        <v>67</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.5">
@@ -2239,23 +2295,21 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="C12" s="4">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>15</v>
+        <v>107</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>131</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.5">
@@ -2263,21 +2317,23 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C13" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="2"/>
+        <v>124</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>123</v>
+      </c>
       <c r="G13" s="2" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.5">
@@ -2285,23 +2341,21 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="C14" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>134</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
-        <v>173</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.5">
@@ -2309,23 +2363,23 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>206</v>
+        <v>40</v>
       </c>
       <c r="C15" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.5">
@@ -2333,21 +2387,23 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>51</v>
+        <v>189</v>
       </c>
       <c r="C16" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F16" s="2"/>
+        <v>42</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>125</v>
+      </c>
       <c r="G16" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.5">
@@ -2355,21 +2411,21 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="C17" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>136</v>
+        <v>5</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>137</v>
+        <v>55</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.5">
@@ -2377,21 +2433,21 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F18" s="5"/>
+      <c r="D18" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.5">
@@ -2399,23 +2455,21 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>201</v>
+        <v>27</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>202</v>
+        <v>26</v>
+      </c>
+      <c r="F19" s="5"/>
+      <c r="G19" s="2" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.5">
@@ -2423,23 +2477,23 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>207</v>
+        <v>54</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>111</v>
+        <v>185</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.5">
@@ -2447,23 +2501,23 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>64</v>
+        <v>190</v>
       </c>
       <c r="C21" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D21" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>66</v>
+      <c r="D21" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.5">
@@ -2471,23 +2525,23 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="C22" s="4">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>179</v>
+        <v>1</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>169</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.5">
@@ -2495,23 +2549,23 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>180</v>
+        <v>38</v>
       </c>
       <c r="C23" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>176</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.5">
@@ -2519,23 +2573,23 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="C24" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>186</v>
+        <v>12</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>193</v>
+        <v>131</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>142</v>
+        <v>172</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.5">
@@ -2543,21 +2597,23 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="C25" s="4">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F25" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="G25" s="2" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.5">
@@ -2565,71 +2621,93 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="C26" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>25</v>
+        <v>179</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>11</v>
+        <v>180</v>
       </c>
       <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
+      <c r="G26" s="2" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A27" s="6">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="C27" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>182</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A28" s="6">
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A29" s="6">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="4">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D28" s="2" t="s">
+      <c r="C29" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="D30" s="17"/>
+      <c r="F29" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="D31" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
@@ -2673,7 +2751,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="G1" s="11" t="s">
         <v>2</v>
@@ -2684,7 +2762,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C2" s="4">
         <f t="shared" ref="C2:C20" si="0">LEN(B2) - LEN(SUBSTITUTE(B2,",",""))+1</f>
@@ -2694,13 +2772,13 @@
         <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>117</v>
+        <v>198</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>14</v>
+        <v>199</v>
       </c>
       <c r="I2" s="14"/>
     </row>
@@ -2709,23 +2787,23 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>6</v>
+        <v>203</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>121</v>
+        <v>204</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
       <c r="I3" s="14"/>
     </row>
@@ -2734,23 +2812,23 @@
         <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>6</v>
+        <v>203</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>119</v>
+        <v>206</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="I4" s="14"/>
     </row>
@@ -2759,7 +2837,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="0"/>
@@ -2767,13 +2845,13 @@
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="I5" s="14"/>
     </row>
@@ -2782,7 +2860,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="0"/>
@@ -2792,13 +2870,13 @@
         <v>37</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>104</v>
+        <v>210</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="I6" s="14"/>
     </row>
@@ -2807,7 +2885,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="0"/>
@@ -2817,13 +2895,13 @@
         <v>41</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>102</v>
+        <v>208</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="I7" s="14"/>
     </row>
@@ -2832,7 +2910,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C8" s="4">
         <f t="shared" si="0"/>
@@ -2842,11 +2920,11 @@
         <v>5</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I8" s="14"/>
     </row>
@@ -2855,21 +2933,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="10" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="I9" s="14"/>
     </row>
@@ -2878,7 +2956,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" si="0"/>
@@ -2901,21 +2979,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C11" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>57</v>
+        <v>200</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>58</v>
+        <v>201</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>62</v>
+        <v>202</v>
       </c>
       <c r="I11" s="14"/>
     </row>
@@ -2924,7 +3002,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C12" s="4">
         <f t="shared" si="0"/>
@@ -2932,13 +3010,13 @@
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I12" s="14"/>
     </row>
@@ -2947,7 +3025,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C13" s="4">
         <f t="shared" si="0"/>
@@ -2957,13 +3035,13 @@
         <v>56</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="I13" s="14"/>
     </row>
@@ -2972,7 +3050,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C14" s="4">
         <f t="shared" si="0"/>
@@ -2982,13 +3060,13 @@
         <v>56</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="I14" s="14"/>
     </row>
@@ -2997,7 +3075,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C15" s="4">
         <f t="shared" si="0"/>
@@ -3007,13 +3085,13 @@
         <v>56</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="I15" s="14"/>
     </row>
@@ -3022,7 +3100,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C16" s="4">
         <f t="shared" si="0"/>
@@ -3032,13 +3110,13 @@
         <v>56</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I16" s="14"/>
     </row>
@@ -3047,7 +3125,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C17" s="4">
         <f t="shared" si="0"/>
@@ -3057,13 +3135,13 @@
         <v>56</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="I17" s="14"/>
     </row>
@@ -3072,21 +3150,23 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D18" s="10"/>
+      <c r="D18" s="10" t="s">
+        <v>217</v>
+      </c>
       <c r="E18" s="10" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>71</v>
+        <v>218</v>
       </c>
       <c r="I18" s="14"/>
     </row>
@@ -3095,23 +3175,23 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>198</v>
+        <v>138</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>216</v>
       </c>
       <c r="I19" s="14"/>
     </row>
@@ -3120,21 +3200,21 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E20" s="2">
         <v>32208551</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I20" s="14"/>
     </row>
@@ -3172,7 +3252,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29DEB476-5E39-423C-AF88-04DFCBED1BF1}">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="3.7265625" style="7" bestFit="1" customWidth="1"/>
@@ -3183,7 +3263,7 @@
     <col min="7" max="16384" width="11" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="18" t="s">
         <v>29</v>
       </c>
@@ -3200,15 +3280,15 @@
         <v>4</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.5">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A2" s="6">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C2" s="4">
         <f t="shared" ref="C2:C6" si="0">LEN(B2) - LEN(SUBSTITUTE(B2,",",""))+1</f>
@@ -3218,13 +3298,16 @@
         <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>117</v>
+        <v>198</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.5">
+        <v>136</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -3239,11 +3322,14 @@
         <v>43</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="G3" s="7" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A4" s="6">
         <v>3</v>
       </c>
@@ -3258,16 +3344,19 @@
         <v>43</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.5">
+      <c r="G4" s="7" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A5" s="6">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="0"/>
@@ -3277,13 +3366,16 @@
         <v>43</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.5">
+        <v>137</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A6" s="6">
         <v>5</v>
       </c>
@@ -3295,44 +3387,47 @@
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.5">
+        <v>183</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.5">
       <c r="F7" s="8"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.5">
       <c r="D8" s="17"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.5">
       <c r="F9" s="8"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.5">
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.5">
       <c r="F11" s="8"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.5">
       <c r="F12" s="8"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.5">
       <c r="F13" s="8"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.5">
       <c r="F14" s="8"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.5">
       <c r="F15" s="8"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.5">
       <c r="F16" s="8"/>
     </row>
     <row r="17" spans="6:6" x14ac:dyDescent="0.5">

--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git_repositories\mlogger\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3F54E0-BF74-4705-B323-07018ED874D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C09F96A7-E7AC-426F-98C8-54526C6DC3FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42600" yWindow="2050" windowWidth="28800" windowHeight="15200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="42060" yWindow="3660" windowWidth="28800" windowHeight="15200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="4" r:id="rId1"/>
@@ -18,8 +18,8 @@
     <sheet name="th_plobe" sheetId="6" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">main!$A$1:$F$29</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">th_plobe!$A$1:$F$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">main!$A$1:$F$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">th_plobe!$A$1:$F$7</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">vel_plobe!$A$1:$F$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="220">
   <si>
     <t>Designator</t>
     <phoneticPr fontId="18" type="noConversion"/>
@@ -160,10 +160,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>CN601</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>ICA01</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -216,18 +212,10 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>IC901</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>TCR2EF30,LM</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>ICB01</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>D801</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -268,9 +256,6 @@
     <t>Microchip Technology</t>
   </si>
   <si>
-    <t>MCP6V02-E/MD</t>
-  </si>
-  <si>
     <t>RB160M-60</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -343,10 +328,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>PN1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>R9</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -447,13 +428,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>JST Sales America Inc.</t>
-  </si>
-  <si>
-    <t>CB01, C901B</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>ICD01</t>
     <phoneticPr fontId="19"/>
   </si>
@@ -553,10 +527,6 @@
   </si>
   <si>
     <t>EXB-28V103JX</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>SH4</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -702,10 +672,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.digikey.jp/ja/products/detail/jst-sales-america-inc/SM04B-SRSS-TB/926710</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>https://www.digikey.jp/ja/products/detail/digi/XB3-24Z8CM-J/7688710</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -804,10 +770,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>SM04B-SRSS-TB</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>C804, C805</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -816,10 +778,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>J02</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>https://www.digikey.jp/ja/products/detail/te-connectivity-passive-product/RQ73C1J232RBTD/9480531</t>
     <phoneticPr fontId="19"/>
   </si>
@@ -941,6 +899,42 @@
   </si>
   <si>
     <t>BAT1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>AVR128DB32-I/RXB</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C3225665.html</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SV2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>IC901, ICB01</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>RN1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>IC801</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>C901B, CB01, CB02</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCP6V02-E/MD</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>SV1</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -2022,7 +2016,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50CA3BD8-2779-45F6-AE49-6AE2C3B11080}">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="3.7265625" style="7" bestFit="1" customWidth="1"/>
@@ -2051,7 +2045,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="G1" s="16" t="s">
         <v>2</v>
@@ -2062,20 +2056,20 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="C2" s="4">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.5">
@@ -2083,20 +2077,20 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C3" s="4">
-        <f t="shared" ref="C2:C29" si="0">LEN(B3) - LEN(SUBSTITUTE(B3,",",""))+1</f>
+        <f t="shared" ref="C3:C28" si="0">LEN(B3) - LEN(SUBSTITUTE(B3,",",""))+1</f>
         <v>6</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>14</v>
@@ -2107,7 +2101,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="0"/>
@@ -2117,10 +2111,10 @@
         <v>6</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>17</v>
@@ -2131,23 +2125,23 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.5">
@@ -2155,7 +2149,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="0"/>
@@ -2165,13 +2159,13 @@
         <v>6</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.5">
@@ -2179,7 +2173,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="0"/>
@@ -2189,13 +2183,13 @@
         <v>6</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.5">
@@ -2217,7 +2211,7 @@
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.5">
@@ -2225,21 +2219,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.5">
@@ -2247,7 +2241,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" si="0"/>
@@ -2257,13 +2251,13 @@
         <v>15</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.5">
@@ -2271,7 +2265,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" s="4">
         <f t="shared" si="0"/>
@@ -2281,10 +2275,10 @@
         <v>15</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>16</v>
@@ -2295,21 +2289,21 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C12" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.5">
@@ -2317,7 +2311,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" s="4">
         <f t="shared" si="0"/>
@@ -2327,13 +2321,13 @@
         <v>15</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.5">
@@ -2363,23 +2357,23 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="4">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E15" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.5">
@@ -2387,23 +2381,23 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="C16" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.5">
@@ -2411,7 +2405,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C17" s="4">
         <f t="shared" si="0"/>
@@ -2421,11 +2415,11 @@
         <v>5</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.5">
@@ -2433,21 +2427,21 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.5">
@@ -2455,7 +2449,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="0"/>
@@ -2469,7 +2463,7 @@
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="2" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.5">
@@ -2477,23 +2471,23 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.5">
@@ -2501,23 +2495,23 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>190</v>
+        <v>56</v>
       </c>
       <c r="C21" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>161</v>
+      <c r="D21" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.5">
@@ -2525,23 +2519,23 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C22" s="4">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>169</v>
+        <v>3</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>161</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.5">
@@ -2549,23 +2543,23 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>38</v>
+        <v>162</v>
       </c>
       <c r="C23" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>48</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.5">
@@ -2573,20 +2567,20 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>171</v>
+        <v>69</v>
       </c>
       <c r="C24" s="4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>12</v>
+        <v>168</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>131</v>
+        <v>173</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>172</v>
+        <v>126</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>167</v>
@@ -2597,23 +2591,21 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="C25" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>134</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.5">
@@ -2621,93 +2613,71 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="C26" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>179</v>
+        <v>25</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>180</v>
+        <v>11</v>
       </c>
       <c r="F26" s="2"/>
-      <c r="G26" s="2" t="s">
-        <v>181</v>
-      </c>
+      <c r="G26" s="2"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A27" s="6">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="C27" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A28" s="6">
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="C28" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>175</v>
+        <v>10</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>174</v>
+        <v>127</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A29" s="6">
-        <v>28</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" s="4">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="D31" s="17"/>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="D30" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
@@ -2751,7 +2721,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="G1" s="11" t="s">
         <v>2</v>
@@ -2762,7 +2732,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C2" s="4">
         <f t="shared" ref="C2:C20" si="0">LEN(B2) - LEN(SUBSTITUTE(B2,",",""))+1</f>
@@ -2772,13 +2742,13 @@
         <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="I2" s="14"/>
     </row>
@@ -2787,23 +2757,23 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="I3" s="14"/>
     </row>
@@ -2812,23 +2782,23 @@
         <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="I4" s="14"/>
     </row>
@@ -2837,7 +2807,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="0"/>
@@ -2845,13 +2815,13 @@
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I5" s="14"/>
     </row>
@@ -2860,23 +2830,23 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="I6" s="14"/>
     </row>
@@ -2885,23 +2855,23 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="I7" s="14"/>
     </row>
@@ -2910,7 +2880,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C8" s="4">
         <f t="shared" si="0"/>
@@ -2920,11 +2890,11 @@
         <v>5</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="I8" s="14"/>
     </row>
@@ -2933,21 +2903,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>58</v>
+        <v>218</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="10" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="I9" s="14"/>
     </row>
@@ -2956,7 +2926,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" si="0"/>
@@ -2979,21 +2949,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C11" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="I11" s="14"/>
     </row>
@@ -3002,7 +2972,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C12" s="4">
         <f t="shared" si="0"/>
@@ -3010,13 +2980,13 @@
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="I12" s="14"/>
     </row>
@@ -3025,23 +2995,23 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C13" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I13" s="14"/>
     </row>
@@ -3050,23 +3020,23 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C14" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="I14" s="14"/>
     </row>
@@ -3075,23 +3045,23 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C15" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="I15" s="14"/>
     </row>
@@ -3100,23 +3070,23 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C16" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="I16" s="14"/>
     </row>
@@ -3125,23 +3095,23 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C17" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="I17" s="14"/>
     </row>
@@ -3150,23 +3120,23 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="I18" s="14"/>
     </row>
@@ -3175,23 +3145,23 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>77</v>
+        <v>219</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="I19" s="14"/>
     </row>
@@ -3200,21 +3170,21 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E20" s="2">
         <v>32208551</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="I20" s="14"/>
     </row>
@@ -3252,7 +3222,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29DEB476-5E39-423C-AF88-04DFCBED1BF1}">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="3.7265625" style="7" bestFit="1" customWidth="1"/>
@@ -3280,7 +3250,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.5">
@@ -3288,23 +3258,23 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>104</v>
+        <v>217</v>
       </c>
       <c r="C2" s="4">
-        <f t="shared" ref="C2:C6" si="0">LEN(B2) - LEN(SUBSTITUTE(B2,",",""))+1</f>
-        <v>2</v>
+        <f t="shared" ref="C2:C7" si="0">LEN(B2) - LEN(SUBSTITUTE(B2,",",""))+1</f>
+        <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.5">
@@ -3312,21 +3282,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>44</v>
+        <v>216</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>159</v>
+        <v>211</v>
       </c>
       <c r="F3" s="2"/>
-      <c r="G3" s="7" t="s">
-        <v>196</v>
+      <c r="G3" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.5">
@@ -3334,21 +3304,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>46</v>
+        <v>214</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="7" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.5">
@@ -3356,23 +3326,23 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.5">
@@ -3380,33 +3350,54 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>30</v>
+        <v>215</v>
       </c>
       <c r="C6" s="4">
-        <f t="shared" si="0"/>
+        <f>LEN(B6) - LEN(SUBSTITUTE(B6,",",""))+1</f>
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>212</v>
+        <v>12</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>215</v>
+        <v>124</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>216</v>
+        <v>163</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="F7" s="8"/>
+      <c r="A7" s="6">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C7" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="D8" s="17"/>
       <c r="F8" s="8"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="D9" s="17"/>
       <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.5">
@@ -3495,6 +3486,9 @@
     </row>
     <row r="38" spans="6:6" x14ac:dyDescent="0.5">
       <c r="F38" s="8"/>
+    </row>
+    <row r="39" spans="6:6" x14ac:dyDescent="0.5">
+      <c r="F39" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="19"/>

--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git_repositories\mlogger\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C09F96A7-E7AC-426F-98C8-54526C6DC3FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA2892C-B226-4972-9252-703767AC3923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42060" yWindow="3660" windowWidth="28800" windowHeight="15200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38730" yWindow="5510" windowWidth="28800" windowHeight="15200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="4" r:id="rId1"/>
@@ -304,10 +304,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>D803, D804, D805</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>C101, C803, C807, C808, CA01, CC01</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -898,10 +894,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>BAT1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>AVR128DB32-I/RXB</t>
     <phoneticPr fontId="19"/>
   </si>
@@ -935,6 +927,14 @@
   </si>
   <si>
     <t>SV1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>BT1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>D803, D804</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -2045,7 +2045,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G1" s="16" t="s">
         <v>2</v>
@@ -2056,20 +2056,20 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C2" s="4">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.5">
@@ -2077,7 +2077,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" ref="C3:C28" si="0">LEN(B3) - LEN(SUBSTITUTE(B3,",",""))+1</f>
@@ -2087,10 +2087,10 @@
         <v>6</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>14</v>
@@ -2101,7 +2101,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="0"/>
@@ -2111,10 +2111,10 @@
         <v>6</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>17</v>
@@ -2125,7 +2125,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="0"/>
@@ -2135,10 +2135,10 @@
         <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>38</v>
@@ -2149,7 +2149,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="0"/>
@@ -2159,13 +2159,13 @@
         <v>6</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.5">
@@ -2183,10 +2183,10 @@
         <v>6</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>65</v>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.5">
@@ -2219,21 +2219,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.5">
@@ -2251,10 +2251,10 @@
         <v>15</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>46</v>
@@ -2275,10 +2275,10 @@
         <v>15</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>16</v>
@@ -2289,14 +2289,14 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>67</v>
+        <v>219</v>
       </c>
       <c r="C12" s="4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>55</v>
@@ -2321,10 +2321,10 @@
         <v>15</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>47</v>
@@ -2370,10 +2370,10 @@
         <v>43</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.5">
@@ -2381,7 +2381,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C16" s="4">
         <f t="shared" si="0"/>
@@ -2394,10 +2394,10 @@
         <v>41</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.5">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.5">
@@ -2434,14 +2434,14 @@
         <v>1</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.5">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.5">
@@ -2478,16 +2478,16 @@
         <v>1</v>
       </c>
       <c r="D20" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>176</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.5">
@@ -2508,7 +2508,7 @@
         <v>57</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>58</v>
@@ -2529,10 +2529,10 @@
         <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>45</v>
@@ -2543,7 +2543,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C23" s="4">
         <f t="shared" si="0"/>
@@ -2553,13 +2553,13 @@
         <v>12</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.5">
@@ -2567,23 +2567,23 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C24" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.5">
@@ -2598,14 +2598,14 @@
         <v>1</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>171</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.5">
@@ -2643,13 +2643,13 @@
         <v>50</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.5">
@@ -2670,10 +2670,10 @@
         <v>10</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.5">
@@ -2721,7 +2721,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G1" s="11" t="s">
         <v>2</v>
@@ -2732,7 +2732,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C2" s="4">
         <f t="shared" ref="C2:C20" si="0">LEN(B2) - LEN(SUBSTITUTE(B2,",",""))+1</f>
@@ -2742,13 +2742,13 @@
         <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>188</v>
       </c>
       <c r="I2" s="14"/>
     </row>
@@ -2757,23 +2757,23 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>194</v>
       </c>
       <c r="I3" s="14"/>
     </row>
@@ -2782,23 +2782,23 @@
         <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="I4" s="14"/>
     </row>
@@ -2807,7 +2807,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="0"/>
@@ -2815,13 +2815,13 @@
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I5" s="14"/>
     </row>
@@ -2830,7 +2830,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="0"/>
@@ -2840,13 +2840,13 @@
         <v>36</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="I6" s="14"/>
     </row>
@@ -2855,7 +2855,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="0"/>
@@ -2865,13 +2865,13 @@
         <v>40</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>198</v>
       </c>
       <c r="I7" s="14"/>
     </row>
@@ -2880,7 +2880,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C8" s="4">
         <f t="shared" si="0"/>
@@ -2890,11 +2890,11 @@
         <v>5</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I8" s="14"/>
     </row>
@@ -2903,7 +2903,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="0"/>
@@ -2913,11 +2913,11 @@
         <v>54</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I9" s="14"/>
     </row>
@@ -2926,7 +2926,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" si="0"/>
@@ -2949,21 +2949,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C11" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D11" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>189</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>190</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I11" s="14"/>
     </row>
@@ -2972,7 +2972,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C12" s="4">
         <f t="shared" si="0"/>
@@ -2980,13 +2980,13 @@
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I12" s="14"/>
     </row>
@@ -2995,7 +2995,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C13" s="4">
         <f t="shared" si="0"/>
@@ -3005,10 +3005,10 @@
         <v>53</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>60</v>
@@ -3020,7 +3020,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C14" s="4">
         <f t="shared" si="0"/>
@@ -3030,13 +3030,13 @@
         <v>53</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I14" s="14"/>
     </row>
@@ -3045,7 +3045,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C15" s="4">
         <f t="shared" si="0"/>
@@ -3055,13 +3055,13 @@
         <v>53</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I15" s="14"/>
     </row>
@@ -3070,7 +3070,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C16" s="4">
         <f t="shared" si="0"/>
@@ -3080,13 +3080,13 @@
         <v>53</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I16" s="14"/>
     </row>
@@ -3095,7 +3095,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C17" s="4">
         <f t="shared" si="0"/>
@@ -3105,13 +3105,13 @@
         <v>53</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I17" s="14"/>
     </row>
@@ -3120,23 +3120,23 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D18" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="I18" s="14"/>
     </row>
@@ -3145,23 +3145,23 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>203</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I19" s="14"/>
     </row>
@@ -3170,7 +3170,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="0"/>
@@ -3250,7 +3250,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.5">
@@ -3258,7 +3258,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C2" s="4">
         <f t="shared" ref="C2:C7" si="0">LEN(B2) - LEN(SUBSTITUTE(B2,",",""))+1</f>
@@ -3268,13 +3268,13 @@
         <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.5">
@@ -3282,7 +3282,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" si="0"/>
@@ -3292,11 +3292,11 @@
         <v>5</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.5">
@@ -3304,7 +3304,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="0"/>
@@ -3314,11 +3314,11 @@
         <v>42</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.5">
@@ -3326,7 +3326,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="0"/>
@@ -3336,13 +3336,13 @@
         <v>42</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.5">
@@ -3350,7 +3350,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C6" s="4">
         <f>LEN(B6) - LEN(SUBSTITUTE(B6,",",""))+1</f>
@@ -3360,13 +3360,13 @@
         <v>12</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.5">
@@ -3374,23 +3374,23 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>204</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.5">

--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git_repositories\mlogger\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA2892C-B226-4972-9252-703767AC3923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E75F25D6-15E9-431E-AC0B-40CC4610470A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38730" yWindow="5510" windowWidth="28800" windowHeight="15200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git_repositories\mlogger\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E75F25D6-15E9-431E-AC0B-40CC4610470A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B06E849D-F0E1-4CDF-90C8-55C9DD565EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38730" yWindow="5510" windowWidth="28800" windowHeight="15200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="47140" yWindow="1750" windowWidth="28440" windowHeight="18120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="4" r:id="rId1"/>
@@ -2125,23 +2125,23 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C5" s="4">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>LEN(B5) - LEN(SUBSTITUTE(B5,",",""))+1</f>
+        <v>3</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.5">
@@ -2149,23 +2149,23 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>177</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>156</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.5">
@@ -2173,23 +2173,23 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>64</v>
+        <v>177</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>65</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.5">
@@ -2197,21 +2197,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="C8" s="4">
-        <f t="shared" si="0"/>
+        <f>LEN(B8) - LEN(SUBSTITUTE(B8,",",""))+1</f>
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>182</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>28</v>
+        <v>183</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>153</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.5">
@@ -2219,21 +2219,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>182</v>
+        <v>9</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>183</v>
+        <v>28</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.5">
